--- a/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-03T20:30:38+00:00</t>
+    <t>2026-05-03T21:28:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-03T21:28:00+00:00</t>
+    <t>2026-05-04T06:23:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T06:23:23+00:00</t>
+    <t>2026-05-04T06:44:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T06:44:52+00:00</t>
+    <t>2026-05-04T07:06:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:06:34+00:00</t>
+    <t>2026-05-04T07:30:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:30:32+00:00</t>
+    <t>2026-05-04T07:50:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:50:36+00:00</t>
+    <t>2026-05-04T08:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:11:13+00:00</t>
+    <t>2026-05-04T08:32:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:32:13+00:00</t>
+    <t>2026-05-04T09:30:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T09:30:07+00:00</t>
+    <t>2026-05-04T09:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T09:51:52+00:00</t>
+    <t>2026-05-04T11:25:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T11:25:12+00:00</t>
+    <t>2026-05-04T11:47:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T11:47:21+00:00</t>
+    <t>2026-05-04T12:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T12:11:06+00:00</t>
+    <t>2026-05-04T13:22:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:22:07+00:00</t>
+    <t>2026-05-04T13:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:47:49+00:00</t>
+    <t>2026-05-04T14:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:15:24+00:00</t>
+    <t>2026-05-04T14:55:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:55:41+00:00</t>
+    <t>2026-05-04T15:18:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T15:18:17+00:00</t>
+    <t>2026-05-04T15:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T18:43:40+00:00</t>
+    <t>2026-05-12T08:39:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-observation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$66</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2588" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2720" uniqueCount="522">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T08:39:42+00:00</t>
+    <t>2026-05-12T14:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -235,6 +235,12 @@
   </si>
   <si>
     <t>Constraint(s)</t>
+  </si>
+  <si>
+    <t>Mapping: BIH LM Senologie</t>
+  </si>
+  <si>
+    <t>Mapping: LM-Element: BildgebungMamma</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -1985,7 +1991,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP66"/>
+  <dimension ref="A1:AR66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
@@ -2023,12 +2029,14 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.35546875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="38.5390625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="212.10546875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2158,6 +2166,12 @@
       <c r="AP1" t="s" s="1">
         <v>78</v>
       </c>
+      <c r="AQ1" t="s" s="1">
+        <v>79</v>
+      </c>
+      <c r="AR1" t="s" s="1">
+        <v>80</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -2168,14 +2182,14 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -2187,16 +2201,16 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -2249,22 +2263,22 @@
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>89</v>
@@ -2273,18 +2287,24 @@
         <v>90</v>
       </c>
       <c r="AO2" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="AP2" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AQ2" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR2" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2292,10 +2312,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -2304,19 +2324,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2366,13 +2386,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -2396,15 +2416,21 @@
         <v>20</v>
       </c>
       <c r="AP3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR3" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2412,10 +2438,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -2424,16 +2450,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2484,19 +2510,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -2514,15 +2540,21 @@
         <v>20</v>
       </c>
       <c r="AP4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR4" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2530,31 +2562,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2604,19 +2636,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2634,15 +2666,21 @@
         <v>20</v>
       </c>
       <c r="AP5" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ5" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR5" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2650,10 +2688,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2665,16 +2703,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2700,13 +2738,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -2724,19 +2762,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2754,26 +2792,32 @@
         <v>20</v>
       </c>
       <c r="AP6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR6" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2785,16 +2829,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2844,19 +2888,19 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -2868,32 +2912,38 @@
         <v>20</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP7" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AQ7" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR7" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2905,16 +2955,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2964,13 +3014,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -2988,32 +3038,38 @@
         <v>20</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP8" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ8" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR8" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -3025,16 +3081,16 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3084,19 +3140,19 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -3108,56 +3164,62 @@
         <v>20</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP9" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR9" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>20</v>
@@ -3206,19 +3268,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -3230,21 +3292,27 @@
         <v>20</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP10" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR10" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3252,10 +3320,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
@@ -3264,20 +3332,20 @@
         <v>20</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -3326,56 +3394,62 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>154</v>
+        <v>20</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>20</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>157</v>
       </c>
       <c r="AP11" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AQ11" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AR11" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -3384,20 +3458,20 @@
         <v>20</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -3446,56 +3520,62 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>20</v>
+        <v>167</v>
       </c>
       <c r="AP12" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AQ12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR12" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -3504,19 +3584,19 @@
         <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3566,45 +3646,51 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>173</v>
+        <v>20</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>175</v>
+        <v>20</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>20</v>
+        <v>176</v>
       </c>
       <c r="AP13" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AQ13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR13" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3612,41 +3698,41 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="S14" t="s" s="2">
         <v>20</v>
@@ -3664,13 +3750,13 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
@@ -3688,25 +3774,25 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>185</v>
+        <v>20</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>186</v>
+        <v>20</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>187</v>
@@ -3718,15 +3804,21 @@
         <v>189</v>
       </c>
       <c r="AP14" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AQ14" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AR14" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3734,10 +3826,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -3749,19 +3841,19 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
@@ -3786,13 +3878,13 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>20</v>
@@ -3810,19 +3902,19 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>20</v>
@@ -3834,56 +3926,62 @@
         <v>20</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="AP15" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AQ15" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AR15" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3908,13 +4006,13 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -3932,25 +4030,25 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>209</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>210</v>
+        <v>20</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>211</v>
@@ -3963,14 +4061,20 @@
       </c>
       <c r="AP16" t="s" s="2">
         <v>214</v>
+      </c>
+      <c r="AQ16" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AR16" t="s" s="2">
+        <v>216</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3978,10 +4082,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -3993,13 +4097,13 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4050,13 +4154,13 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
@@ -4074,32 +4178,38 @@
         <v>20</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP17" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AQ17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR17" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
@@ -4111,16 +4221,16 @@
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4158,31 +4268,31 @@
         <v>20</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>20</v>
@@ -4194,21 +4304,27 @@
         <v>20</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP18" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AQ18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR18" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4216,10 +4332,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -4228,22 +4344,22 @@
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -4280,31 +4396,31 @@
         <v>20</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>20</v>
@@ -4313,37 +4429,43 @@
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>236</v>
+        <v>20</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>237</v>
+        <v>20</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>20</v>
+        <v>238</v>
       </c>
       <c r="AP19" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AQ19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR19" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -4352,22 +4474,22 @@
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -4377,7 +4499,7 @@
         <v>20</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>20</v>
@@ -4416,19 +4538,19 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>20</v>
@@ -4437,37 +4559,43 @@
         <v>20</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>236</v>
+        <v>20</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>237</v>
+        <v>20</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>20</v>
+        <v>238</v>
       </c>
       <c r="AP20" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AQ20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR20" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -4476,22 +4604,22 @@
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -4501,7 +4629,7 @@
         <v>20</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>20</v>
@@ -4540,19 +4668,19 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>20</v>
@@ -4561,37 +4689,43 @@
         <v>20</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>236</v>
+        <v>20</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>237</v>
+        <v>20</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>20</v>
+        <v>238</v>
       </c>
       <c r="AP21" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AQ21" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR21" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -4600,22 +4734,22 @@
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4625,7 +4759,7 @@
         <v>20</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>20</v>
@@ -4664,19 +4798,19 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>20</v>
@@ -4685,37 +4819,43 @@
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>236</v>
+        <v>20</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>237</v>
+        <v>20</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>20</v>
+        <v>238</v>
       </c>
       <c r="AP22" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AQ22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR22" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -4724,22 +4864,22 @@
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4749,7 +4889,7 @@
         <v>20</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>20</v>
@@ -4788,19 +4928,19 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>20</v>
@@ -4809,37 +4949,43 @@
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>236</v>
+        <v>20</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>237</v>
+        <v>20</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>20</v>
+        <v>238</v>
       </c>
       <c r="AP23" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AQ23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR23" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -4848,22 +4994,22 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4873,7 +5019,7 @@
         <v>20</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>20</v>
@@ -4912,19 +5058,19 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>20</v>
@@ -4933,37 +5079,43 @@
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>236</v>
+        <v>20</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>237</v>
+        <v>20</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>20</v>
+        <v>238</v>
       </c>
       <c r="AP24" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AQ24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR24" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -4972,22 +5124,22 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4997,7 +5149,7 @@
         <v>20</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>20</v>
@@ -5036,19 +5188,19 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>20</v>
@@ -5057,37 +5209,43 @@
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>236</v>
+        <v>20</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>237</v>
+        <v>20</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>20</v>
+        <v>238</v>
       </c>
       <c r="AP25" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AQ25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR25" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -5096,22 +5254,22 @@
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -5121,7 +5279,7 @@
         <v>20</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>20</v>
@@ -5160,19 +5318,19 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>20</v>
@@ -5181,37 +5339,43 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>236</v>
+        <v>20</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>237</v>
+        <v>20</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>20</v>
+        <v>238</v>
       </c>
       <c r="AP26" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AQ26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR26" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -5220,22 +5384,22 @@
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5245,7 +5409,7 @@
         <v>20</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>20</v>
@@ -5284,19 +5448,19 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>20</v>
@@ -5305,37 +5469,43 @@
         <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>236</v>
+        <v>20</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>237</v>
+        <v>20</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>20</v>
+        <v>238</v>
       </c>
       <c r="AP27" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AQ27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR27" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -5344,22 +5514,22 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -5369,7 +5539,7 @@
         <v>20</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>20</v>
@@ -5408,19 +5578,19 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>20</v>
@@ -5429,37 +5599,43 @@
         <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>236</v>
+        <v>20</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>237</v>
+        <v>20</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>20</v>
+        <v>238</v>
       </c>
       <c r="AP28" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AQ28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR28" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -5468,22 +5644,22 @@
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5493,7 +5669,7 @@
         <v>20</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>20</v>
@@ -5532,19 +5708,19 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>20</v>
@@ -5553,24 +5729,30 @@
         <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>236</v>
+        <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>237</v>
+        <v>20</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>20</v>
+        <v>238</v>
       </c>
       <c r="AP29" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AQ29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR29" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5578,10 +5760,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5590,22 +5772,22 @@
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5654,19 +5836,19 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
@@ -5675,24 +5857,30 @@
         <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>286</v>
+        <v>20</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>20</v>
+        <v>287</v>
       </c>
       <c r="AP30" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AQ30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR30" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5700,34 +5888,34 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5776,45 +5964,51 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>293</v>
+        <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>295</v>
+        <v>20</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>296</v>
       </c>
       <c r="AP31" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AQ31" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AR31" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5822,10 +6016,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -5834,19 +6028,19 @@
         <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5896,19 +6090,19 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
@@ -5917,35 +6111,41 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>211</v>
+        <v>20</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>302</v>
+        <v>20</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>296</v>
+        <v>213</v>
       </c>
       <c r="AP32" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AQ32" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AR32" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5954,22 +6154,22 @@
         <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -6018,56 +6218,62 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>310</v>
+        <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>312</v>
+        <v>20</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>313</v>
       </c>
       <c r="AP33" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AQ33" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AR33" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -6076,22 +6282,22 @@
         <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -6128,92 +6334,98 @@
         <v>20</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AC34" s="2"/>
       <c r="AD34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>322</v>
+        <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>324</v>
+        <v>20</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>325</v>
       </c>
       <c r="AP34" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AQ34" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AR34" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -6262,45 +6474,51 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>322</v>
+        <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>324</v>
+        <v>20</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>325</v>
       </c>
       <c r="AP35" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AQ35" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AR35" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6308,10 +6526,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -6320,19 +6538,19 @@
         <v>20</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6382,19 +6600,19 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
@@ -6403,24 +6621,30 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>336</v>
+        <v>20</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>337</v>
+        <v>20</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>338</v>
       </c>
       <c r="AP36" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AQ36" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AR36" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6428,10 +6652,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -6440,20 +6664,20 @@
         <v>20</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -6502,45 +6726,51 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>344</v>
+        <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>346</v>
+        <v>20</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>347</v>
       </c>
       <c r="AP37" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AQ37" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AR37" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6548,34 +6778,34 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6624,45 +6854,51 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>355</v>
+        <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>356</v>
+        <v>20</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>357</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>20</v>
+        <v>358</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
+      </c>
+      <c r="AQ38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR38" t="s" s="2">
+        <v>360</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6670,10 +6906,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6685,19 +6921,19 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6722,13 +6958,13 @@
         <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -6746,19 +6982,19 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
@@ -6767,35 +7003,41 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>368</v>
+        <v>20</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AP39" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AQ39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR39" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6807,19 +7049,19 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -6844,13 +7086,13 @@
         <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>20</v>
@@ -6868,45 +7110,51 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>377</v>
+        <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>378</v>
+        <v>20</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>379</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>20</v>
+        <v>380</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
+      </c>
+      <c r="AQ40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR40" t="s" s="2">
+        <v>382</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6914,10 +7162,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6929,19 +7177,19 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6990,19 +7238,19 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
@@ -7011,24 +7259,30 @@
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>387</v>
+        <v>20</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>388</v>
+        <v>20</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>20</v>
+        <v>389</v>
       </c>
       <c r="AP41" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AQ41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR41" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7036,13 +7290,13 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>20</v>
@@ -7051,16 +7305,16 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7086,13 +7340,13 @@
         <v>20</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -7110,45 +7364,51 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>395</v>
+        <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>396</v>
+        <v>20</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>397</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>20</v>
+        <v>398</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
+      </c>
+      <c r="AQ42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR42" t="s" s="2">
+        <v>400</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7156,10 +7416,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -7171,19 +7431,19 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -7208,13 +7468,13 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
@@ -7232,19 +7492,19 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
@@ -7253,24 +7513,30 @@
         <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>406</v>
+        <v>20</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>407</v>
+        <v>20</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>20</v>
+        <v>408</v>
       </c>
       <c r="AP43" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AQ43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR43" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7278,10 +7544,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -7293,16 +7559,16 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7352,45 +7618,51 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>413</v>
+        <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>414</v>
+        <v>20</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>415</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>20</v>
+        <v>416</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
+      </c>
+      <c r="AQ44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR44" t="s" s="2">
+        <v>418</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7398,10 +7670,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -7413,16 +7685,16 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7472,45 +7744,51 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>422</v>
+        <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>423</v>
+        <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>424</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>20</v>
+        <v>425</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
+      </c>
+      <c r="AQ45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR45" t="s" s="2">
+        <v>427</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7518,10 +7796,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -7533,19 +7811,19 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7594,19 +7872,19 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
@@ -7615,24 +7893,30 @@
         <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>433</v>
+        <v>20</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>434</v>
+        <v>20</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>20</v>
+        <v>435</v>
       </c>
       <c r="AP46" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AQ46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR46" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7640,10 +7924,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -7655,13 +7939,13 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7712,13 +7996,13 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
@@ -7736,32 +8020,38 @@
         <v>20</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP47" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AQ47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR47" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -7773,16 +8063,16 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7832,19 +8122,19 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>20</v>
@@ -7856,56 +8146,62 @@
         <v>20</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP48" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AQ48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR48" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7954,19 +8250,19 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>20</v>
@@ -7978,21 +8274,27 @@
         <v>20</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP49" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR49" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8000,10 +8302,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -8015,13 +8317,13 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8072,19 +8374,19 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>20</v>
@@ -8093,24 +8395,30 @@
         <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>447</v>
+        <v>20</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>448</v>
+        <v>20</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>20</v>
+        <v>449</v>
       </c>
       <c r="AP50" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AQ50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR50" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8118,10 +8426,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -8133,13 +8441,13 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8190,45 +8498,51 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AG51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="AP51" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AQ51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR51" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8236,10 +8550,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
@@ -8251,19 +8565,19 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -8288,13 +8602,13 @@
         <v>20</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -8312,45 +8626,51 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>460</v>
+        <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>461</v>
+        <v>20</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>379</v>
+        <v>462</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>20</v>
+        <v>463</v>
       </c>
       <c r="AP52" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AQ52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR52" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8358,10 +8678,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>20</v>
@@ -8373,19 +8693,19 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8410,13 +8730,13 @@
         <v>20</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>20</v>
@@ -8434,45 +8754,51 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="AG53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>379</v>
-      </c>
       <c r="AO53" t="s" s="2">
-        <v>20</v>
+        <v>463</v>
       </c>
       <c r="AP53" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AQ53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR53" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8480,10 +8806,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -8495,17 +8821,17 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8554,19 +8880,19 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>20</v>
@@ -8578,21 +8904,27 @@
         <v>20</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>474</v>
+        <v>20</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP54" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AQ54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR54" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8600,10 +8932,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -8615,13 +8947,13 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8672,19 +9004,19 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
@@ -8693,24 +9025,30 @@
         <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>447</v>
+        <v>20</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>478</v>
+        <v>20</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>20</v>
+        <v>449</v>
       </c>
       <c r="AP55" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AQ55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR55" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8718,10 +9056,10 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
@@ -8730,19 +9068,19 @@
         <v>20</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8792,19 +9130,19 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
@@ -8813,24 +9151,30 @@
         <v>20</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>484</v>
+        <v>20</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>485</v>
+        <v>20</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>20</v>
+        <v>486</v>
       </c>
       <c r="AP56" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AQ56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR56" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8838,10 +9182,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
@@ -8850,19 +9194,19 @@
         <v>20</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8912,45 +9256,51 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="AG57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="AP57" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AQ57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR57" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8958,10 +9308,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>20</v>
@@ -8970,22 +9320,22 @@
         <v>20</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -9034,19 +9384,19 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>20</v>
@@ -9055,24 +9405,30 @@
         <v>20</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>497</v>
+        <v>20</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>498</v>
+        <v>20</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>20</v>
+        <v>499</v>
       </c>
       <c r="AP58" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AQ58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR58" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9080,10 +9436,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
@@ -9095,13 +9451,13 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9152,13 +9508,13 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>20</v>
@@ -9176,32 +9532,38 @@
         <v>20</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP59" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AQ59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR59" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>20</v>
@@ -9213,16 +9575,16 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9272,19 +9634,19 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>20</v>
@@ -9296,56 +9658,62 @@
         <v>20</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP60" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AQ60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR60" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9394,19 +9762,19 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>20</v>
@@ -9418,21 +9786,27 @@
         <v>20</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP61" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR61" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9440,10 +9814,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>20</v>
@@ -9452,22 +9826,22 @@
         <v>20</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -9492,13 +9866,13 @@
         <v>20</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>20</v>
@@ -9516,45 +9890,51 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>506</v>
+        <v>20</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>211</v>
+        <v>20</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>212</v>
+        <v>508</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>213</v>
       </c>
       <c r="AP62" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AQ62" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AR62" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9562,10 +9942,10 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
@@ -9574,22 +9954,22 @@
         <v>20</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -9638,45 +10018,51 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>511</v>
+        <v>20</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>356</v>
+        <v>20</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>357</v>
+        <v>513</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>20</v>
+        <v>358</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
+      </c>
+      <c r="AQ63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR63" t="s" s="2">
+        <v>360</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9684,10 +10070,10 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>20</v>
@@ -9699,19 +10085,19 @@
         <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -9736,13 +10122,13 @@
         <v>20</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>20</v>
@@ -9760,19 +10146,19 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>20</v>
@@ -9781,35 +10167,41 @@
         <v>20</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>368</v>
+        <v>20</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AP64" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AQ64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR64" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>20</v>
@@ -9821,19 +10213,19 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>20</v>
@@ -9858,13 +10250,13 @@
         <v>20</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>20</v>
@@ -9882,45 +10274,51 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>377</v>
+        <v>20</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>378</v>
+        <v>20</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>379</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>20</v>
+        <v>380</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
+      </c>
+      <c r="AQ65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR65" t="s" s="2">
+        <v>382</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9928,10 +10326,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>20</v>
@@ -9943,19 +10341,19 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -10004,19 +10402,19 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>20</v>
@@ -10025,20 +10423,26 @@
         <v>20</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>433</v>
+        <v>20</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>434</v>
+        <v>20</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>20</v>
+        <v>435</v>
       </c>
       <c r="AP66" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AQ66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR66" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP66">
+  <autoFilter ref="A1:AR66">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
